--- a/reports/Daily_Report.xlsx
+++ b/reports/Daily_Report.xlsx
@@ -818,12 +818,12 @@
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>Today I have worked on the development of the Telegram bot, making progress on its functionality and features.</t>
+          <t>Today I have worked on creating a daily task share feature for the automation Telegram bot.</t>
         </is>
       </c>
       <c r="C36" s="16" t="inlineStr">
         <is>
-          <t>Telegram Bot Development</t>
+          <t>Daily Task Automation</t>
         </is>
       </c>
       <c r="D36" s="16" t="inlineStr">
